--- a/questionnaire_templates/016_elderly_mental_wellness_study_participation_form--questionnaire_templates.xlsx
+++ b/questionnaire_templates/016_elderly_mental_wellness_study_participation_form--questionnaire_templates.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -630,7 +630,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>How would you rate your overall sense of wellbeing?</t>
+          <t>Wellbeing Question2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,7 +653,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>How would you rate your overall sense of wellbeing?</t>
+          <t>Wellbeing Question3</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,7 +676,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>How would you rate your overall sense of wellbeing?</t>
+          <t>Wellbeing Question4</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,7 +699,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>How would you rate your overall sense of wellbeing?</t>
+          <t>Wellbeing Question5</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,7 +722,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>How would you rate your overall sense of wellbeing?</t>
+          <t>Wellbeing Question6</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,7 +745,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>How would you rate your overall sense of wellbeing?</t>
+          <t>Wellbeing Question7</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,7 +768,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>How would you rate your overall sense of wellbeing?</t>
+          <t>Wellbeing Question8</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,7 +791,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>How would you rate your overall sense of wellbeing?</t>
+          <t>Wellbeing Question9</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,7 +814,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>How would you rate your overall sense of wellbeing?</t>
+          <t>Wellbeing Question10</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,7 +837,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>How would you rate your overall sense of wellbeing?</t>
+          <t>Wellbeing Question11</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,7 +860,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>How would you rate your overall sense of wellbeing?</t>
+          <t>Wellbeing Question12</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,7 +883,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>How would you rate your overall sense of wellbeing?</t>
+          <t>Wellbeing Question13</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -906,7 +906,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>How would you rate your overall sense of wellbeing?</t>
+          <t>Wellbeing Question14</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -929,7 +929,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>How would you rate your overall sense of wellbeing?</t>
+          <t>Wellbeing Question15</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -952,7 +952,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>How would you rate your overall sense of wellbeing?</t>
+          <t>Wellbeing Question16</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -975,7 +975,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>How would you rate your overall sense of wellbeing?</t>
+          <t>Wellbeing Question17</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -998,7 +998,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>How would you rate your overall sense of wellbeing?</t>
+          <t>Wellbeing Question18</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>How would you rate your overall sense of wellbeing?</t>
+          <t>Wellbeing Question19</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>How would you rate your overall sense of wellbeing?</t>
+          <t>Wellbeing Question20</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>How would you rate your overall sense of wellbeing?</t>
+          <t>Wellbeing Question21</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
